--- a/sheets/민요/검수/꽃이 피었네.xlsx
+++ b/sheets/민요/검수/꽃이 피었네.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,33 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2897,8 +3004,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:K18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -2911,728 +3022,773 @@
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꽃이 피었네 — 민요채보-1/꽃이 피었네.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">꽃이 피었네</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">받</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E4" s="14"/>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I4" s="14"/>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K4" s="14"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">싸</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">앗</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="K5" s="14"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E6" s="15"/>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G6" s="15"/>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I6" s="15"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="15"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">단</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">피</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="C8" s="14"/>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E8" s="14"/>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="I8" s="14"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="14"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">었</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">피</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="C10" s="15"/>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E10" s="15"/>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G10" s="15"/>
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="I10" s="15"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="15"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">문</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">김</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">었</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="12"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="I12" s="14"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="14"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="12"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">밖</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">선</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">건</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2" t="inlineStr">
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="12"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E14" s="15"/>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G14" s="15"/>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I14" s="15"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="15"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="12"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">출</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">달</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="inlineStr">
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="12"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E16" s="14"/>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G16" s="14"/>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I16" s="14"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="14"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="12"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">입</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="12"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E18" s="15"/>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G18" s="15"/>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I18" s="15"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="15"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:K2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/꽃이 피었네.xlsx
+++ b/sheets/민요/검수/꽃이 피었네.xlsx
@@ -259,11 +259,7 @@
           <t xml:space="preserve">쪽</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196</t>
-        </is>
-      </c>
+      <c r="B5" s="4"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -2742,10 +2738,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s=""/>
-      <c r="B1" s="">
-        <v>0</v>
-      </c>
+      <c r="A1" s="0"/>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>

--- a/sheets/민요/검수/꽃이 피었네.xlsx
+++ b/sheets/민요/검수/꽃이 피었네.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -553,13 +553,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -632,13 +632,13 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―南</t>
+          <t xml:space="preserve">無|–南</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -715,13 +715,13 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢―</t>
+          <t xml:space="preserve">潢–</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢―</t>
+          <t xml:space="preserve">潢–</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -942,13 +942,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―南</t>
+          <t xml:space="preserve">無|–南</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1021,13 +1021,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I31" s="2"/>
@@ -1728,13 +1728,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南^|―</t>
+          <t xml:space="preserve">南^|–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南^
-―</t>
+–</t>
         </is>
       </c>
       <c r="I32" s="2"/>
@@ -2159,12 +2159,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―△</t>
+          <t xml:space="preserve">–△</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―△</t>
+          <t xml:space="preserve">–△</t>
         </is>
       </c>
       <c r="I45" s="2"/>
@@ -2313,12 +2313,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢</t>
+          <t xml:space="preserve">–潢</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢</t>
+          <t xml:space="preserve">–潢</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2352,13 +2352,13 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|―</t>
+          <t xml:space="preserve">㳞|–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2431,13 +2431,13 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2510,13 +2510,13 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―南</t>
+          <t xml:space="preserve">無|–南</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2668,13 +2668,13 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―</t>
+          <t xml:space="preserve">–|–</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="I56" s="2"/>
@@ -2762,7 +2762,7 @@
       <c r="B3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -2795,7 +2795,7 @@
       <c r="H3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
@@ -2856,7 +2856,7 @@
       <c r="B5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -2889,7 +2889,7 @@
       <c r="H5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -2983,7 +2983,7 @@
       <c r="H7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -3035,8 +3035,8 @@
       <c r="A9" s="0"/>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="C9" s="9"/>
@@ -3157,7 +3157,7 @@
       <c r="C12" s="9"/>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢―</t>
+          <t xml:space="preserve">潢–</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -3217,7 +3217,7 @@
       <c r="H13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -3234,7 +3234,7 @@
       <c r="C14" s="10"/>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―△</t>
+          <t xml:space="preserve">–△</t>
         </is>
       </c>
       <c r="E14" s="10"/>
@@ -3290,7 +3290,7 @@
       <c r="H15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
@@ -3307,7 +3307,7 @@
       <c r="C16" s="9"/>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢</t>
+          <t xml:space="preserve">–潢</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G16" s="9"/>
@@ -3337,7 +3337,7 @@
       <c r="D17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -3348,7 +3348,7 @@
       <c r="F17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南^
-―</t>
+–</t>
         </is>
       </c>
       <c r="G17" s="9"/>

--- a/sheets/민요/검수/꽃이 피었네.xlsx
+++ b/sheets/민요/검수/꽃이 피었네.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2742,654 +2780,654 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃이 피었네</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 潢</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">삭주단</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">건너</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="J3" s="17"/>
-      <c r="K3" s="8"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="22"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">싸</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌㴌</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">마을</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J4" s="17"/>
-      <c r="K4" s="9"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="23"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –南</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">내사</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 無南</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">받아썼다</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">김선</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –南</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">피</t>
         </is>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="9"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="23"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無⌝</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">仲㳞</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">달네</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無⌝</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">었</t>
         </is>
       </c>
-      <c r="J6" s="17"/>
-      <c r="K6" s="10"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="27"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 ·</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南無
 無</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">문밖출</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
 湳</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">큰애</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="8"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="22"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="C8" s="23"/>
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">입</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="9"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="23"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="23"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 無南</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">안한다</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">湳㴌
 㳞</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J9" s="17"/>
-      <c r="K9" s="9"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="23"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="27"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">굴</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="10"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="27"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南無
 無</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">니나</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無潢</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">홍도</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="J11" s="17"/>
-      <c r="K11" s="8"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="22"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="B12" s="21"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢–</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J12" s="17"/>
-      <c r="K12" s="9"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="23"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="B13" s="21"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">난실</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑仲</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">화피</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –南</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">피</t>
         </is>
       </c>
-      <c r="J13" s="17"/>
-      <c r="K13" s="9"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="23"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="B14" s="21"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–△</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="27"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">었</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">었</t>
         </is>
       </c>
-      <c r="J14" s="17"/>
-      <c r="K14" s="10"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="27"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">니나</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 ·</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="J15" s="17"/>
-      <c r="K15" s="8"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="22"/>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="B16" s="21"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–潢</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="G16" s="23"/>
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="9"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="23"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="B17" s="21"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 –</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^
 –</t>
         </is>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="G17" s="23"/>
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^
 ·</t>
         </is>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="9"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="23"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="B18" s="21"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="27"/>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="10"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/꽃이 피었네.xlsx
+++ b/sheets/민요/검수/꽃이 피었네.xlsx
@@ -2763,22 +2763,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="60.41" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="60.41" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
       <c r="J3" s="21"/>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="60.41" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       <c r="J4" s="21"/>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="60.41" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
       <c r="J5" s="21"/>
       <c r="K5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="60.41" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="24" t="inlineStr">
         <is>
@@ -2983,12 +2983,12 @@
       <c r="J6" s="21"/>
       <c r="K6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="60.41" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-·</t>
+–</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -3032,11 +3032,11 @@
       <c r="J7" s="21"/>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="60.41" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C8" s="23"/>
@@ -3062,14 +3062,14 @@
       </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="23"/>
       <c r="J8" s="21"/>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="60.41" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
       <c r="J9" s="21"/>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="60.41" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
       <c r="J10" s="21"/>
       <c r="K10" s="27"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="60.41" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -3189,7 +3189,7 @@
       <c r="J11" s="21"/>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="60.41" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -3226,7 +3226,7 @@
       <c r="J12" s="21"/>
       <c r="K12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="60.41" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3266,7 +3266,7 @@
       <c r="J13" s="21"/>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="60.41" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="27"/>
@@ -3299,7 +3299,7 @@
       <c r="J14" s="21"/>
       <c r="K14" s="27"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="60.41" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -3317,7 +3317,7 @@
       <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-·</t>
+–</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -3339,7 +3339,7 @@
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="60.41" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -3361,14 +3361,14 @@
       <c r="G16" s="23"/>
       <c r="H16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I16" s="23"/>
       <c r="J16" s="21"/>
       <c r="K16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="60.41" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -3393,14 +3393,14 @@
       <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^
-·</t>
+–</t>
         </is>
       </c>
       <c r="I17" s="23"/>
       <c r="J17" s="21"/>
       <c r="K17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="60.41" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="27"/>

--- a/sheets/민요/검수/꽃이 피었네.xlsx
+++ b/sheets/민요/검수/꽃이 피었네.xlsx
@@ -2816,7 +2816,9 @@
       </c>
       <c r="E3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">삭주단</t>
+          <t xml:space="preserve">삭
+주
+단</t>
         </is>
       </c>
       <c r="F3" s="21" t="inlineStr">
@@ -2827,7 +2829,8 @@
       </c>
       <c r="G3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">건너</t>
+          <t xml:space="preserve">건
+너</t>
         </is>
       </c>
       <c r="H3" s="21" t="inlineStr">
@@ -2873,7 +2876,8 @@
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">마을</t>
+          <t xml:space="preserve">마
+을</t>
         </is>
       </c>
       <c r="H4" s="21" t="inlineStr">
@@ -2899,7 +2903,8 @@
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">내사</t>
+          <t xml:space="preserve">내
+사</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -2910,7 +2915,10 @@
       </c>
       <c r="E5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">받아썼다</t>
+          <t xml:space="preserve">받
+아
+썼
+다</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -2921,7 +2929,8 @@
       </c>
       <c r="G5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">김선</t>
+          <t xml:space="preserve">김
+선</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -2967,7 +2976,8 @@
       </c>
       <c r="G6" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">달네</t>
+          <t xml:space="preserve">달
+네</t>
         </is>
       </c>
       <c r="H6" s="24" t="inlineStr">
@@ -3004,7 +3014,9 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">문밖출</t>
+          <t xml:space="preserve">문
+밖
+출</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -3015,7 +3027,8 @@
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">큰애</t>
+          <t xml:space="preserve">큰
+애</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -3086,7 +3099,9 @@
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">안한다</t>
+          <t xml:space="preserve">안
+한
+다</t>
         </is>
       </c>
       <c r="F9" s="24" t="inlineStr">
@@ -3162,7 +3177,8 @@
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">니나</t>
+          <t xml:space="preserve">니
+나</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -3173,7 +3189,8 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">홍도</t>
+          <t xml:space="preserve">홍
+도</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -3238,7 +3255,8 @@
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">난실</t>
+          <t xml:space="preserve">난
+실</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -3249,7 +3267,8 @@
       </c>
       <c r="G13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">화피</t>
+          <t xml:space="preserve">화
+피</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -3311,7 +3330,8 @@
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">니나</t>
+          <t xml:space="preserve">니
+나</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">

--- a/sheets/민요/검수/꽃이 피었네.xlsx
+++ b/sheets/민요/검수/꽃이 피었네.xlsx
@@ -477,7 +477,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -488,7 +487,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -502,7 +500,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -513,7 +510,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -529,7 +525,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -540,7 +535,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -560,7 +554,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -570,7 +563,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -585,7 +577,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -596,7 +587,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -612,7 +602,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -623,7 +612,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -639,7 +627,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -650,7 +637,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -664,7 +650,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -675,7 +660,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -685,7 +669,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -696,7 +679,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -712,7 +694,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -723,7 +704,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -738,7 +718,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -749,7 +728,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -765,7 +743,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -774,7 +751,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -783,7 +759,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -792,7 +767,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -806,7 +780,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -816,7 +789,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -826,7 +798,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -837,7 +808,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -852,7 +822,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -863,7 +832,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -877,7 +845,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -887,7 +854,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -898,7 +864,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -909,7 +874,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -923,7 +887,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -934,7 +897,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -949,7 +911,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -960,7 +921,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -970,7 +930,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -981,7 +940,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -991,7 +949,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1001,7 +958,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -1012,7 +968,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1022,7 +977,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -1038,7 +992,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -1047,17 +1001,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -1090,6 +1044,12 @@
       <sz val="24"/>
       <name val="궁서체"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1182,7 +1142,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1236,6 +1196,46 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3430,233 +3430,233 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="15" width="6"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="7" t="s">
+      <c r="B3" s="17"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="18" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="7" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="19" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="7" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="18" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="7" t="s">
+      <c r="B6" s="17"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="7" t="s">
+      <c r="E6" s="19"/>
+      <c r="F6" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="19" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="7" t="s">
+      <c r="B7" s="17"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="18" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="7" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="19" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="7" t="s">
+      <c r="B9" s="17"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="18" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="13" t="s">
+      <c r="B10" s="17"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="H10" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="13" t="s">
+      <c r="I10" s="22"/>
+      <c r="J10" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="K10" s="12"/>
+      <c r="K10" s="22"/>
     </row>
     <row r="11" ht="87.31" customHeight="true"/>
     <row r="12" ht="87.31" customHeight="true"/>

--- a/sheets/민요/검수/꽃이 피었네.xlsx
+++ b/sheets/민요/검수/꽃이 피었네.xlsx
@@ -1066,10 +1066,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/꽃이 피었네.xlsx
+++ b/sheets/민요/검수/꽃이 피었네.xlsx
@@ -475,46 +475,18 @@
 –</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑
+    <t xml:space="preserve">姑
 –
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+南</t>
   </si>
   <si>
     <t xml:space="preserve">얼
 싸</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無潢
+    <t xml:space="preserve">無潢
 潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+潢</t>
   </si>
   <si>
     <t xml:space="preserve">삭
@@ -523,23 +495,9 @@
 자</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
+    <t xml:space="preserve">潢
 㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌㴌</t>
-    </r>
+㴌㴌</t>
   </si>
   <si>
     <t xml:space="preserve">건
@@ -552,22 +510,8 @@
 이</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無
-–南</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
+    <t xml:space="preserve">無
+–南無</t>
   </si>
   <si>
     <t xml:space="preserve">내
@@ -575,23 +519,9 @@
 랑</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無潢
+    <t xml:space="preserve">無潢
 無南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
+仲</t>
   </si>
   <si>
     <t xml:space="preserve">받
@@ -600,23 +530,9 @@
 고</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞
+    <t xml:space="preserve">㳞
 㳞
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㳞㳞</t>
-    </r>
+㳞㳞</t>
   </si>
   <si>
     <t xml:space="preserve">김
@@ -625,65 +541,23 @@
 네</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無
+    <t xml:space="preserve">無
 –南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
+無</t>
   </si>
   <si>
     <t xml:space="preserve">피
 었</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
+    <t xml:space="preserve">南
 –
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南無
+–</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南無
 無
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無潢</t>
-    </r>
+無潢</t>
   </si>
   <si>
     <t xml:space="preserve">문
@@ -692,23 +566,9 @@
 입</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">湳
+    <t xml:space="preserve">湳
 湳
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">湳</t>
-    </r>
+湳</t>
   </si>
   <si>
     <t xml:space="preserve">큰
@@ -716,23 +576,9 @@
 기</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
+    <t xml:space="preserve">–
 –
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
+△</t>
   </si>
   <si>
     <t xml:space="preserve">안
@@ -741,78 +587,21 @@
 네</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">湳</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無湳
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
+    <t xml:space="preserve">湳無湳
+㳞㴌</t>
   </si>
   <si>
     <t xml:space="preserve">얼
 굴</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南^
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南無
+    <t xml:space="preserve">南^
+△</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南無
 無
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–南</t>
-    </r>
+–南</t>
   </si>
   <si>
     <t xml:space="preserve">니
@@ -820,88 +609,32 @@
 노</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
+    <t xml:space="preserve">潢
 無潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無南</t>
-    </r>
+無南</t>
   </si>
   <si>
     <t xml:space="preserve">홍
 도</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢
+    <t xml:space="preserve">潢
+潢
 –</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
+  </si>
+  <si>
+    <t xml:space="preserve">潢
 潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
+△</t>
   </si>
   <si>
     <t xml:space="preserve">난
 실</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲
+    <t xml:space="preserve">仲
 姑仲
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">姑仲</t>
-    </r>
+姑仲</t>
   </si>
   <si>
     <t xml:space="preserve">화
@@ -909,80 +642,24 @@
 었</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無
+    <t xml:space="preserve">無
 –南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢無</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞
+潢無</t>
+  </si>
+  <si>
+    <t xml:space="preserve">㳞
 㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–潢</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㳞
+–潢</t>
+  </si>
+  <si>
+    <t xml:space="preserve">㳞
 –
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南^
+㴌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南^
 –
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
+△</t>
   </si>
 </sst>
 </file>
@@ -3421,7 +3098,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B2:K1048576"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -3439,7 +3116,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="15" width="6"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="43.48" customHeight="true">
       <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
@@ -3453,7 +3131,7 @@
       <c r="J2" s="16"/>
       <c r="K2" s="16"/>
     </row>
-    <row r="3" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
       <c r="B3" s="17"/>
       <c r="C3" s="18"/>
       <c r="D3" s="17" t="s">
@@ -3481,7 +3159,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
       <c r="B4" s="17"/>
       <c r="C4" s="19"/>
       <c r="D4" s="17" t="s">
@@ -3509,7 +3187,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
       <c r="B5" s="17"/>
       <c r="C5" s="18"/>
       <c r="D5" s="17" t="s">
@@ -3537,7 +3215,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
       <c r="B6" s="17"/>
       <c r="C6" s="19"/>
       <c r="D6" s="17" t="s">
@@ -3563,7 +3241,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
       <c r="B7" s="17"/>
       <c r="C7" s="18"/>
       <c r="D7" s="17"/>
@@ -3587,7 +3265,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
       <c r="B8" s="17"/>
       <c r="C8" s="19"/>
       <c r="D8" s="17"/>
@@ -3611,7 +3289,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
       <c r="B9" s="17"/>
       <c r="C9" s="18"/>
       <c r="D9" s="17"/>
@@ -3635,7 +3313,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="87.31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
       <c r="B10" s="17"/>
       <c r="C10" s="22"/>
       <c r="D10" s="17"/>
@@ -3655,14 +3333,6 @@
       </c>
       <c r="K10" s="22"/>
     </row>
-    <row r="11" ht="87.31" customHeight="true"/>
-    <row r="12" ht="87.31" customHeight="true"/>
-    <row r="13" ht="87.31" customHeight="true"/>
-    <row r="14" ht="87.31" customHeight="true"/>
-    <row r="15" ht="87.31" customHeight="true"/>
-    <row r="16" ht="87.31" customHeight="true"/>
-    <row r="17" ht="87.31" customHeight="true"/>
-    <row r="18" ht="87.31" customHeight="true"/>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3674,7 +3344,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="77" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="92"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/꽃이 피었네.xlsx
+++ b/sheets/민요/검수/꽃이 피었네.xlsx
@@ -3104,20 +3104,20 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="15" width="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="43.48" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="51.28" customHeight="true">
       <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
@@ -3131,7 +3131,7 @@
       <c r="J2" s="16"/>
       <c r="K2" s="16"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.37" customHeight="true">
       <c r="B3" s="17"/>
       <c r="C3" s="18"/>
       <c r="D3" s="17" t="s">
@@ -3159,7 +3159,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.37" customHeight="true">
       <c r="B4" s="17"/>
       <c r="C4" s="19"/>
       <c r="D4" s="17" t="s">
@@ -3187,7 +3187,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.37" customHeight="true">
       <c r="B5" s="17"/>
       <c r="C5" s="18"/>
       <c r="D5" s="17" t="s">
@@ -3215,7 +3215,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.37" customHeight="true">
       <c r="B6" s="17"/>
       <c r="C6" s="19"/>
       <c r="D6" s="17" t="s">
@@ -3241,7 +3241,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.37" customHeight="true">
       <c r="B7" s="17"/>
       <c r="C7" s="18"/>
       <c r="D7" s="17"/>
@@ -3265,7 +3265,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.37" customHeight="true">
       <c r="B8" s="17"/>
       <c r="C8" s="19"/>
       <c r="D8" s="17"/>
@@ -3289,7 +3289,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.37" customHeight="true">
       <c r="B9" s="17"/>
       <c r="C9" s="18"/>
       <c r="D9" s="17"/>
@@ -3313,7 +3313,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.85" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="114.37" customHeight="true">
       <c r="B10" s="17"/>
       <c r="C10" s="22"/>
       <c r="D10" s="17"/>
@@ -3344,7 +3344,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="92"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="78"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
